--- a/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI.xlsx
+++ b/resources/report/60/95/ex_imp/TID_121_VAT INVOICE_MULTI.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SKYPE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvthe\OneDrive\Máy tính\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45D88F1-14EF-408B-8B4D-01A97A40EA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="45" windowWidth="18090" windowHeight="9990" tabRatio="754"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VAT. Multi Rate" sheetId="25" r:id="rId1"/>
+    <sheet name="Invoice" sheetId="25" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -687,7 +688,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1290,410 +1291,401 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1729,7 +1721,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27991" name="Picture 2"/>
+        <xdr:cNvPr id="27991" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000576D0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -2047,7 +2045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R57"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2073,320 +2071,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:18" s="9" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="148" t="s">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="151" t="s">
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="151"/>
-      <c r="O2" s="153"/>
-      <c r="P2" s="153"/>
-      <c r="Q2" s="153"/>
-      <c r="R2" s="34"/>
-    </row>
-    <row r="3" spans="1:18" s="9" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="149"/>
-      <c r="K3" s="149"/>
-      <c r="L3" s="149"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="36"/>
-    </row>
-    <row r="4" spans="1:18" s="9" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="149"/>
-      <c r="K4" s="149"/>
-      <c r="L4" s="149"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="36"/>
-    </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="35"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="150" t="s">
+      <c r="N2" s="153"/>
+      <c r="O2" s="142"/>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="142"/>
+      <c r="R2" s="31"/>
+    </row>
+    <row r="3" spans="1:18" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="33"/>
+    </row>
+    <row r="4" spans="1:18" s="7" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="70"/>
+      <c r="R4" s="33"/>
+    </row>
+    <row r="5" spans="1:18" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="32"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="150"/>
-      <c r="H5" s="150"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="150"/>
-      <c r="K5" s="150"/>
-      <c r="L5" s="150"/>
-      <c r="M5" s="88" t="s">
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="151" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="88"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="36"/>
-    </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="75"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="36"/>
+      <c r="N5" s="151"/>
+      <c r="O5" s="154"/>
+      <c r="P5" s="154"/>
+      <c r="Q5" s="154"/>
+      <c r="R5" s="33"/>
+    </row>
+    <row r="6" spans="1:18" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="33"/>
     </row>
     <row r="7" spans="1:18" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="142" t="s">
+      <c r="A7" s="34"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="142"/>
-      <c r="H7" s="142"/>
-      <c r="I7" s="142"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="38"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="151"/>
+      <c r="N7" s="151"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="35"/>
     </row>
     <row r="8" spans="1:18" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="87" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="87"/>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="80"/>
-      <c r="Q8" s="80"/>
-      <c r="R8" s="38"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="75"/>
+      <c r="R8" s="35"/>
     </row>
     <row r="9" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="39"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="39"/>
+      <c r="A10" s="34"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="24" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="152"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="152"/>
-      <c r="K11" s="152"/>
-      <c r="L11" s="152"/>
-      <c r="M11" s="152"/>
-      <c r="N11" s="152"/>
-      <c r="O11" s="152"/>
-      <c r="P11" s="152"/>
-      <c r="Q11" s="152"/>
-      <c r="R11" s="39"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="141"/>
+      <c r="O11" s="141"/>
+      <c r="P11" s="141"/>
+      <c r="Q11" s="141"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="24" t="s">
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="72"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="39"/>
-    </row>
-    <row r="13" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
+      <c r="R12" s="36"/>
+    </row>
+    <row r="13" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
       <c r="B13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="24" t="s">
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-      <c r="M13" s="141"/>
-      <c r="N13" s="141"/>
-      <c r="O13" s="141"/>
-      <c r="P13" s="141"/>
-      <c r="Q13" s="141"/>
-      <c r="R13" s="39"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="34"/>
+      <c r="B14" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="141"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="40"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="1:18" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="40"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="76"/>
+      <c r="P15" s="76"/>
+      <c r="Q15" s="76"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -2403,940 +2381,830 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="39"/>
-    </row>
-    <row r="17" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="41"/>
+      <c r="R16" s="36"/>
+    </row>
+    <row r="17" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="37"/>
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="143"/>
-      <c r="K17" s="143"/>
-      <c r="L17" s="143"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="143"/>
-      <c r="O17" s="143"/>
-      <c r="P17" s="143"/>
-      <c r="Q17" s="143"/>
-      <c r="R17" s="42"/>
-    </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="41"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="134"/>
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="38"/>
+    </row>
+    <row r="18" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="37"/>
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="141"/>
-      <c r="H18" s="141"/>
-      <c r="I18" s="141"/>
-      <c r="J18" s="141"/>
-      <c r="K18" s="141"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="141"/>
-      <c r="N18" s="141"/>
-      <c r="O18" s="141"/>
-      <c r="P18" s="141"/>
-      <c r="Q18" s="141"/>
-      <c r="R18" s="42"/>
-    </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="41"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="38"/>
+    </row>
+    <row r="19" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="37"/>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="42"/>
-    </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="41"/>
+      <c r="R19" s="38"/>
+    </row>
+    <row r="20" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="37"/>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="156"/>
-      <c r="E20" s="156"/>
-      <c r="F20" s="156"/>
-      <c r="G20" s="156"/>
-      <c r="H20" s="156"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="156"/>
-      <c r="K20" s="156"/>
-      <c r="L20" s="156"/>
-      <c r="M20" s="156"/>
-      <c r="N20" s="156"/>
-      <c r="O20" s="156"/>
-      <c r="P20" s="156"/>
-      <c r="Q20" s="156"/>
-      <c r="R20" s="42"/>
-    </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="41"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="145"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="38"/>
+    </row>
+    <row r="21" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="37"/>
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="42"/>
-    </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="41"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="38"/>
+    </row>
+    <row r="22" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="37"/>
       <c r="B22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="42"/>
-    </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="41"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="38"/>
+    </row>
+    <row r="23" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="37"/>
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="73" t="s">
+      <c r="L23" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="42"/>
+      <c r="R23" s="38"/>
     </row>
     <row r="24" spans="1:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="39"/>
-    </row>
-    <row r="25" spans="1:18" s="58" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="54"/>
-      <c r="B25" s="55" t="s">
+      <c r="A24" s="34"/>
+      <c r="R24" s="36"/>
+    </row>
+    <row r="25" spans="1:18" s="54" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="50"/>
+      <c r="B25" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="157" t="s">
+      <c r="C25" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="55" t="s">
+      <c r="D25" s="148"/>
+      <c r="E25" s="148"/>
+      <c r="F25" s="148"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="70" t="s">
+      <c r="I25" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="157" t="s">
+      <c r="J25" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="158"/>
-      <c r="L25" s="55" t="s">
+      <c r="K25" s="147"/>
+      <c r="L25" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="M25" s="56" t="s">
+      <c r="M25" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="N25" s="56" t="s">
+      <c r="N25" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="O25" s="157" t="s">
+      <c r="O25" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="P25" s="159"/>
-      <c r="Q25" s="158"/>
-      <c r="R25" s="57"/>
-    </row>
-    <row r="26" spans="1:18" s="62" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="59"/>
-      <c r="B26" s="60" t="s">
+      <c r="P25" s="148"/>
+      <c r="Q25" s="147"/>
+      <c r="R25" s="53"/>
+    </row>
+    <row r="26" spans="1:18" s="58" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="55"/>
+      <c r="B26" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="60" t="s">
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="60" t="s">
+      <c r="I26" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="81" t="s">
+      <c r="J26" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="83"/>
-      <c r="L26" s="60" t="s">
+      <c r="K26" s="79"/>
+      <c r="L26" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="M26" s="69" t="s">
+      <c r="M26" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="N26" s="69" t="s">
+      <c r="N26" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="O26" s="81" t="s">
+      <c r="O26" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="P26" s="82"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="61"/>
-    </row>
-    <row r="27" spans="1:18" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
-      <c r="B27" s="6">
+      <c r="P26" s="78"/>
+      <c r="Q26" s="79"/>
+      <c r="R26" s="57"/>
+    </row>
+    <row r="27" spans="1:18" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="40"/>
+      <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="84">
+      <c r="C27" s="138">
         <v>2</v>
       </c>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="6">
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="4">
         <v>3</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="4">
         <v>4</v>
       </c>
-      <c r="J27" s="84">
+      <c r="J27" s="138">
         <v>5</v>
       </c>
-      <c r="K27" s="85"/>
-      <c r="L27" s="6" t="s">
+      <c r="K27" s="140"/>
+      <c r="L27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M27" s="49">
+      <c r="M27" s="45">
         <v>7</v>
       </c>
-      <c r="N27" s="49">
+      <c r="N27" s="45">
         <v>8</v>
       </c>
-      <c r="O27" s="84" t="s">
+      <c r="O27" s="138" t="s">
         <v>29</v>
       </c>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="85"/>
-      <c r="R27" s="76"/>
-    </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="94" t="s">
+      <c r="P27" s="139"/>
+      <c r="Q27" s="140"/>
+      <c r="R27" s="71"/>
+    </row>
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="41"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="96"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="154"/>
-      <c r="K28" s="155"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="144"/>
-      <c r="P28" s="145"/>
-      <c r="Q28" s="146"/>
-      <c r="R28" s="77"/>
-    </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="45"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="101"/>
-      <c r="K29" s="102"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="138"/>
-      <c r="Q29" s="139"/>
-      <c r="R29" s="77"/>
-    </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="45"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="91"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="101"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="138"/>
-      <c r="Q30" s="139"/>
-      <c r="R30" s="77"/>
-    </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="45"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="138"/>
-      <c r="Q31" s="139"/>
-      <c r="R31" s="77"/>
-    </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="45"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="101"/>
-      <c r="K32" s="102"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="137"/>
-      <c r="P32" s="138"/>
-      <c r="Q32" s="139"/>
-      <c r="R32" s="77"/>
-    </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="45"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="102"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="52"/>
-      <c r="O33" s="137"/>
-      <c r="P33" s="138"/>
-      <c r="Q33" s="139"/>
-      <c r="R33" s="77"/>
-    </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="45"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="52"/>
-      <c r="O34" s="137"/>
-      <c r="P34" s="138"/>
-      <c r="Q34" s="139"/>
-      <c r="R34" s="77"/>
-    </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="45"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="91"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="101"/>
-      <c r="K35" s="102"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="137"/>
-      <c r="P35" s="138"/>
-      <c r="Q35" s="139"/>
-      <c r="R35" s="77"/>
-    </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="45"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="91"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="92"/>
-      <c r="F36" s="92"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="101"/>
-      <c r="K36" s="102"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="137"/>
-      <c r="P36" s="138"/>
-      <c r="Q36" s="139"/>
-      <c r="R36" s="77"/>
-    </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="45"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="93"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="101"/>
-      <c r="K37" s="102"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="137"/>
-      <c r="P37" s="138"/>
-      <c r="Q37" s="139"/>
-      <c r="R37" s="77"/>
-    </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="45"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="99"/>
-      <c r="E38" s="99"/>
-      <c r="F38" s="99"/>
-      <c r="G38" s="100"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="103"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53"/>
-      <c r="O38" s="130"/>
-      <c r="P38" s="131"/>
-      <c r="Q38" s="132"/>
-      <c r="R38" s="77"/>
-    </row>
-    <row r="39" spans="1:18" s="65" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="63"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="H39" s="136" t="s">
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="143"/>
+      <c r="K28" s="144"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="135"/>
+      <c r="P28" s="136"/>
+      <c r="Q28" s="137"/>
+      <c r="R28" s="72"/>
+    </row>
+    <row r="29" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="41"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="94"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="130"/>
+      <c r="P29" s="131"/>
+      <c r="Q29" s="132"/>
+      <c r="R29" s="72"/>
+    </row>
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="41"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="130"/>
+      <c r="P30" s="131"/>
+      <c r="Q30" s="132"/>
+      <c r="R30" s="72"/>
+    </row>
+    <row r="31" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="41"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="94"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="130"/>
+      <c r="P31" s="131"/>
+      <c r="Q31" s="132"/>
+      <c r="R31" s="72"/>
+    </row>
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="41"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="85"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="94"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
+      <c r="O32" s="130"/>
+      <c r="P32" s="131"/>
+      <c r="Q32" s="132"/>
+      <c r="R32" s="72"/>
+    </row>
+    <row r="33" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="41"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="84"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="94"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
+      <c r="O33" s="130"/>
+      <c r="P33" s="131"/>
+      <c r="Q33" s="132"/>
+      <c r="R33" s="72"/>
+    </row>
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="41"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="94"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="48"/>
+      <c r="O34" s="130"/>
+      <c r="P34" s="131"/>
+      <c r="Q34" s="132"/>
+      <c r="R34" s="72"/>
+    </row>
+    <row r="35" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="41"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="85"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="94"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="130"/>
+      <c r="P35" s="131"/>
+      <c r="Q35" s="132"/>
+      <c r="R35" s="72"/>
+    </row>
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="41"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="93"/>
+      <c r="K36" s="94"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="48"/>
+      <c r="N36" s="48"/>
+      <c r="O36" s="130"/>
+      <c r="P36" s="131"/>
+      <c r="Q36" s="132"/>
+      <c r="R36" s="72"/>
+    </row>
+    <row r="37" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="41"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="93"/>
+      <c r="K37" s="94"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="130"/>
+      <c r="P37" s="131"/>
+      <c r="Q37" s="132"/>
+      <c r="R37" s="72"/>
+    </row>
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="41"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="91"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="95"/>
+      <c r="K38" s="96"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="49"/>
+      <c r="N38" s="49"/>
+      <c r="O38" s="124"/>
+      <c r="P38" s="125"/>
+      <c r="Q38" s="126"/>
+      <c r="R38" s="72"/>
+    </row>
+    <row r="39" spans="1:18" s="61" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="59"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="H39" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="136"/>
-      <c r="L39" s="133" t="s">
+      <c r="I39" s="97"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="M39" s="134"/>
-      <c r="N39" s="135"/>
-      <c r="O39" s="133" t="s">
+      <c r="M39" s="128"/>
+      <c r="N39" s="129"/>
+      <c r="O39" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="135"/>
-      <c r="R39" s="78"/>
-    </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="41"/>
-      <c r="B40" s="66" t="s">
+      <c r="P39" s="128"/>
+      <c r="Q39" s="129"/>
+      <c r="R39" s="73"/>
+    </row>
+    <row r="40" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="37"/>
+      <c r="B40" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="97"/>
-      <c r="I40" s="97"/>
-      <c r="J40" s="97"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="122"/>
-      <c r="M40" s="123"/>
-      <c r="N40" s="124"/>
-      <c r="O40" s="122"/>
-      <c r="P40" s="123"/>
-      <c r="Q40" s="124"/>
-      <c r="R40" s="42"/>
-    </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="41"/>
-      <c r="B41" s="66" t="s">
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="118"/>
+      <c r="M40" s="119"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="118"/>
+      <c r="P40" s="119"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="38"/>
+    </row>
+    <row r="41" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="37"/>
+      <c r="B41" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="97"/>
-      <c r="I41" s="97"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="97"/>
-      <c r="L41" s="122"/>
-      <c r="M41" s="123"/>
-      <c r="N41" s="124"/>
-      <c r="O41" s="122"/>
-      <c r="P41" s="123"/>
-      <c r="Q41" s="124"/>
-      <c r="R41" s="42"/>
-    </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="41"/>
-      <c r="B42" s="66" t="s">
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="89"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="118"/>
+      <c r="M41" s="119"/>
+      <c r="N41" s="120"/>
+      <c r="O41" s="118"/>
+      <c r="P41" s="119"/>
+      <c r="Q41" s="120"/>
+      <c r="R41" s="38"/>
+    </row>
+    <row r="42" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="37"/>
+      <c r="B42" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="97"/>
-      <c r="I42" s="97"/>
-      <c r="J42" s="97"/>
-      <c r="K42" s="97"/>
-      <c r="L42" s="122"/>
-      <c r="M42" s="123"/>
-      <c r="N42" s="124"/>
-      <c r="O42" s="122"/>
-      <c r="P42" s="123"/>
-      <c r="Q42" s="124"/>
-      <c r="R42" s="42"/>
-    </row>
-    <row r="43" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="41"/>
-      <c r="B43" s="66" t="s">
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="89"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="89"/>
+      <c r="K42" s="89"/>
+      <c r="L42" s="118"/>
+      <c r="M42" s="119"/>
+      <c r="N42" s="120"/>
+      <c r="O42" s="118"/>
+      <c r="P42" s="119"/>
+      <c r="Q42" s="120"/>
+      <c r="R42" s="38"/>
+    </row>
+    <row r="43" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="37"/>
+      <c r="B43" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="97"/>
-      <c r="I43" s="97"/>
-      <c r="J43" s="97"/>
-      <c r="K43" s="97"/>
-      <c r="L43" s="122"/>
-      <c r="M43" s="123"/>
-      <c r="N43" s="124"/>
-      <c r="O43" s="122"/>
-      <c r="P43" s="123"/>
-      <c r="Q43" s="124"/>
-      <c r="R43" s="42"/>
-    </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="41"/>
-      <c r="B44" s="66" t="s">
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="89"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="89"/>
+      <c r="K43" s="89"/>
+      <c r="L43" s="118"/>
+      <c r="M43" s="119"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="118"/>
+      <c r="P43" s="119"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="38"/>
+    </row>
+    <row r="44" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="37"/>
+      <c r="B44" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="97"/>
-      <c r="I44" s="97"/>
-      <c r="J44" s="97"/>
-      <c r="K44" s="97"/>
-      <c r="L44" s="122"/>
-      <c r="M44" s="123"/>
-      <c r="N44" s="124"/>
-      <c r="O44" s="122"/>
-      <c r="P44" s="123"/>
-      <c r="Q44" s="124"/>
-      <c r="R44" s="42"/>
-    </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="41"/>
-      <c r="B45" s="67" t="s">
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="89"/>
+      <c r="L44" s="118"/>
+      <c r="M44" s="119"/>
+      <c r="N44" s="120"/>
+      <c r="O44" s="118"/>
+      <c r="P44" s="119"/>
+      <c r="Q44" s="120"/>
+      <c r="R44" s="38"/>
+    </row>
+    <row r="45" spans="1:18" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="37"/>
+      <c r="B45" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="97"/>
-      <c r="I45" s="97"/>
-      <c r="J45" s="97"/>
-      <c r="K45" s="97"/>
-      <c r="L45" s="125"/>
-      <c r="M45" s="126"/>
-      <c r="N45" s="127"/>
-      <c r="O45" s="125"/>
-      <c r="P45" s="126"/>
-      <c r="Q45" s="127"/>
-      <c r="R45" s="42"/>
-    </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="41"/>
-      <c r="B46" s="31" t="s">
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="89"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="89"/>
+      <c r="K45" s="89"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="122"/>
+      <c r="N45" s="123"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="122"/>
+      <c r="Q45" s="123"/>
+      <c r="R45" s="38"/>
+    </row>
+    <row r="46" spans="1:18" s="2" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="37"/>
+      <c r="B46" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="128"/>
-      <c r="I46" s="128"/>
-      <c r="J46" s="128"/>
-      <c r="K46" s="128"/>
-      <c r="L46" s="128"/>
-      <c r="M46" s="128"/>
-      <c r="N46" s="128"/>
-      <c r="O46" s="128"/>
-      <c r="P46" s="128"/>
-      <c r="Q46" s="129"/>
-      <c r="R46" s="42"/>
-    </row>
-    <row r="47" spans="1:18" s="13" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="46"/>
-      <c r="B47" s="105" t="s">
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="116"/>
+      <c r="I46" s="116"/>
+      <c r="J46" s="116"/>
+      <c r="K46" s="116"/>
+      <c r="L46" s="116"/>
+      <c r="M46" s="116"/>
+      <c r="N46" s="116"/>
+      <c r="O46" s="116"/>
+      <c r="P46" s="116"/>
+      <c r="Q46" s="117"/>
+      <c r="R46" s="38"/>
+    </row>
+    <row r="47" spans="1:18" s="11" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="42"/>
+      <c r="B47" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="105"/>
-      <c r="D47" s="105"/>
-      <c r="E47" s="105"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="105"/>
-      <c r="H47" s="105"/>
-      <c r="I47" s="105"/>
-      <c r="J47" s="105"/>
-      <c r="K47" s="105" t="s">
+      <c r="C47" s="98"/>
+      <c r="D47" s="98"/>
+      <c r="E47" s="98"/>
+      <c r="F47" s="98"/>
+      <c r="G47" s="98"/>
+      <c r="H47" s="98"/>
+      <c r="I47" s="98"/>
+      <c r="J47" s="98"/>
+      <c r="K47" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="L47" s="105"/>
-      <c r="M47" s="105"/>
-      <c r="N47" s="105"/>
-      <c r="O47" s="105"/>
-      <c r="P47" s="105"/>
-      <c r="Q47" s="105"/>
-      <c r="R47" s="47"/>
+      <c r="L47" s="98"/>
+      <c r="M47" s="98"/>
+      <c r="N47" s="98"/>
+      <c r="O47" s="98"/>
+      <c r="P47" s="98"/>
+      <c r="Q47" s="98"/>
+      <c r="R47" s="43"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="37"/>
-      <c r="B48" s="106" t="s">
+      <c r="A48" s="34"/>
+      <c r="B48" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="106"/>
-      <c r="D48" s="106"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="107"/>
-      <c r="H48" s="107"/>
-      <c r="I48" s="107"/>
-      <c r="J48" s="107"/>
-      <c r="K48" s="107" t="s">
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="100"/>
+      <c r="H48" s="100"/>
+      <c r="I48" s="100"/>
+      <c r="J48" s="100"/>
+      <c r="K48" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="L48" s="107"/>
-      <c r="M48" s="107"/>
-      <c r="N48" s="107"/>
-      <c r="O48" s="107"/>
-      <c r="P48" s="107"/>
-      <c r="Q48" s="107"/>
-      <c r="R48" s="43"/>
+      <c r="L48" s="100"/>
+      <c r="M48" s="100"/>
+      <c r="N48" s="100"/>
+      <c r="O48" s="100"/>
+      <c r="P48" s="100"/>
+      <c r="Q48" s="100"/>
+      <c r="R48" s="39"/>
     </row>
     <row r="49" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="37"/>
-      <c r="B49" s="111" t="s">
+      <c r="A49" s="34"/>
+      <c r="B49" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="111"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="111"/>
-      <c r="F49" s="111"/>
-      <c r="G49" s="111"/>
-      <c r="H49" s="111"/>
-      <c r="I49" s="111"/>
-      <c r="J49" s="111"/>
-      <c r="K49" s="111" t="s">
+      <c r="C49" s="104"/>
+      <c r="D49" s="104"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="104"/>
+      <c r="G49" s="104"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="104"/>
+      <c r="J49" s="104"/>
+      <c r="K49" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="111"/>
-      <c r="M49" s="111"/>
-      <c r="N49" s="111"/>
-      <c r="O49" s="111"/>
-      <c r="P49" s="111"/>
-      <c r="Q49" s="111"/>
-      <c r="R49" s="40"/>
+      <c r="L49" s="104"/>
+      <c r="M49" s="104"/>
+      <c r="N49" s="104"/>
+      <c r="O49" s="104"/>
+      <c r="P49" s="104"/>
+      <c r="Q49" s="104"/>
+      <c r="R49" s="36"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="37"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="39"/>
+      <c r="A50" s="34"/>
+      <c r="R50" s="36"/>
     </row>
     <row r="51" spans="1:18" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="37"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="112" t="s">
+      <c r="A51" s="34"/>
+      <c r="K51" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="L51" s="113"/>
-      <c r="M51" s="113"/>
-      <c r="N51" s="113"/>
-      <c r="O51" s="113"/>
-      <c r="P51" s="113"/>
-      <c r="Q51" s="114"/>
-      <c r="R51" s="39"/>
+      <c r="L51" s="106"/>
+      <c r="M51" s="106"/>
+      <c r="N51" s="106"/>
+      <c r="O51" s="106"/>
+      <c r="P51" s="106"/>
+      <c r="Q51" s="107"/>
+      <c r="R51" s="36"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="37"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="115" t="s">
+      <c r="A52" s="34"/>
+      <c r="B52" s="25"/>
+      <c r="K52" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="L52" s="116"/>
-      <c r="M52" s="116"/>
-      <c r="N52" s="116"/>
-      <c r="O52" s="116"/>
-      <c r="P52" s="116"/>
-      <c r="Q52" s="117"/>
-      <c r="R52" s="39"/>
+      <c r="L52" s="109"/>
+      <c r="M52" s="109"/>
+      <c r="N52" s="109"/>
+      <c r="O52" s="109"/>
+      <c r="P52" s="109"/>
+      <c r="Q52" s="110"/>
+      <c r="R52" s="36"/>
     </row>
     <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="37"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
-      <c r="I53" s="118"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="119" t="s">
+      <c r="A53" s="34"/>
+      <c r="B53" s="26"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="111"/>
+      <c r="F53" s="111"/>
+      <c r="G53" s="111"/>
+      <c r="H53" s="111"/>
+      <c r="I53" s="111"/>
+      <c r="K53" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="L53" s="120"/>
-      <c r="M53" s="120"/>
-      <c r="N53" s="120"/>
-      <c r="O53" s="120"/>
-      <c r="P53" s="120"/>
-      <c r="Q53" s="121"/>
-      <c r="R53" s="39"/>
+      <c r="L53" s="113"/>
+      <c r="M53" s="113"/>
+      <c r="N53" s="113"/>
+      <c r="O53" s="113"/>
+      <c r="P53" s="113"/>
+      <c r="Q53" s="114"/>
+      <c r="R53" s="36"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="37"/>
-      <c r="B54" s="79" t="s">
+      <c r="A54" s="34"/>
+      <c r="B54" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="147"/>
-      <c r="H54" s="147"/>
-      <c r="I54" s="147"/>
-      <c r="J54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="39"/>
+      <c r="G54" s="115"/>
+      <c r="H54" s="115"/>
+      <c r="I54" s="115"/>
+      <c r="P54" s="6"/>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="36"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="37"/>
-      <c r="B55" s="30" t="s">
+      <c r="A55" s="34"/>
+      <c r="B55" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="39"/>
+      <c r="K55" s="26"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="36"/>
     </row>
     <row r="56" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="48"/>
-      <c r="B56" s="108" t="s">
+      <c r="A56" s="44"/>
+      <c r="B56" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="108"/>
-      <c r="D56" s="108"/>
-      <c r="E56" s="108"/>
-      <c r="F56" s="108"/>
-      <c r="G56" s="108"/>
-      <c r="H56" s="108"/>
-      <c r="I56" s="108"/>
-      <c r="J56" s="108"/>
-      <c r="K56" s="108"/>
-      <c r="L56" s="108"/>
-      <c r="M56" s="108"/>
-      <c r="N56" s="108"/>
-      <c r="O56" s="108"/>
-      <c r="P56" s="108"/>
-      <c r="Q56" s="108"/>
-      <c r="R56" s="109"/>
+      <c r="C56" s="101"/>
+      <c r="D56" s="101"/>
+      <c r="E56" s="101"/>
+      <c r="F56" s="101"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="101"/>
+      <c r="I56" s="101"/>
+      <c r="J56" s="101"/>
+      <c r="K56" s="101"/>
+      <c r="L56" s="101"/>
+      <c r="M56" s="101"/>
+      <c r="N56" s="101"/>
+      <c r="O56" s="101"/>
+      <c r="P56" s="101"/>
+      <c r="Q56" s="101"/>
+      <c r="R56" s="102"/>
     </row>
     <row r="57" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="110" t="s">
+      <c r="B57" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="C57" s="110"/>
-      <c r="D57" s="110"/>
-      <c r="E57" s="110"/>
-      <c r="F57" s="110"/>
-      <c r="G57" s="110"/>
-      <c r="H57" s="110"/>
-      <c r="I57" s="110"/>
-      <c r="J57" s="110"/>
-      <c r="K57" s="110"/>
-      <c r="L57" s="110"/>
-      <c r="M57" s="110"/>
-      <c r="N57" s="110"/>
-      <c r="O57" s="110"/>
-      <c r="P57" s="110"/>
-      <c r="Q57" s="110"/>
-      <c r="R57" s="110"/>
+      <c r="C57" s="103"/>
+      <c r="D57" s="103"/>
+      <c r="E57" s="103"/>
+      <c r="F57" s="103"/>
+      <c r="G57" s="103"/>
+      <c r="H57" s="103"/>
+      <c r="I57" s="103"/>
+      <c r="J57" s="103"/>
+      <c r="K57" s="103"/>
+      <c r="L57" s="103"/>
+      <c r="M57" s="103"/>
+      <c r="N57" s="103"/>
+      <c r="O57" s="103"/>
+      <c r="P57" s="103"/>
+      <c r="Q57" s="103"/>
+      <c r="R57" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="100">
@@ -3351,6 +3219,11 @@
     <mergeCell ref="F5:L5"/>
     <mergeCell ref="F6:L6"/>
     <mergeCell ref="M2:N2"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:Q5"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="C31:G31"/>
@@ -3366,6 +3239,7 @@
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="F13:Q13"/>
     <mergeCell ref="F11:Q11"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="O36:Q36"/>
     <mergeCell ref="O33:Q33"/>
@@ -3428,12 +3302,6 @@
     <mergeCell ref="C28:G28"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:G30"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:Q5"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="I15:Q15"/>
     <mergeCell ref="C26:G26"/>
